--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488023_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488023_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.1181</v>
+        <v>-0.722</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.2371</v>
+        <v>-0.8691</v>
       </c>
       <c r="F3" t="n">
-        <v>0.119</v>
+        <v>0.1471</v>
       </c>
       <c r="G3" t="n">
         <v>0.7941</v>
@@ -688,13 +688,13 @@
         <v>0.5947</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5157</v>
+        <v>-1.1196</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8112</v>
+        <v>-0.4432</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7045</v>
+        <v>-0.6765</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.6399</v>
+        <v>-2.0868</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4612</v>
+        <v>0.7897</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.1011</v>
+        <v>-2.8765</v>
       </c>
       <c r="G4" t="n">
         <v>2.0459</v>
@@ -766,13 +766,13 @@
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.8147</v>
+        <v>-3.2615</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.7471</v>
+        <v>-1.4186</v>
       </c>
       <c r="U4" t="n">
-        <v>-2.0676</v>
+        <v>-1.843</v>
       </c>
       <c r="V4" t="n">
         <v>-1.0693</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GUERRERO JONSSON</t>
+          <t>J. GARCIA RAMOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.9968</v>
+        <v>-4.3649</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8927</v>
+        <v>-2.2447</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.1041</v>
+        <v>-2.1202</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5492</v>
+        <v>-2.9603</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8361</v>
+        <v>-0.7658</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3852</v>
+        <v>-2.1945</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4575</v>
+        <v>-1.7956</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1412</v>
+        <v>-0.5177</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5988</v>
+        <v>-1.2779</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0916</v>
+        <v>-1.1647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6948</v>
+        <v>-0.2481</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7864</v>
+        <v>-0.9166</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.4972</v>
+        <v>-3.0578</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.444</v>
+        <v>-0.7157</v>
       </c>
       <c r="U5" t="n">
-        <v>-2.0532</v>
+        <v>-2.3421</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.3468</v>
+        <v>0.0674</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.3468</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. GARCIA RAMOS</t>
+          <t>D. GUERRERO JONSSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-5.1842</v>
+        <v>-4.7773</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8394</v>
+        <v>-1.8697</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3448</v>
+        <v>-2.9075</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9603</v>
+        <v>-0.5492</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7658</v>
+        <v>0.8361</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1945</v>
+        <v>-1.3852</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.7956</v>
+        <v>-0.4575</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5177</v>
+        <v>0.1412</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2779</v>
+        <v>-0.5988</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1647</v>
+        <v>-0.0916</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2481</v>
+        <v>0.6948</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9166</v>
+        <v>-0.7864</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5858</v>
+        <v>1.3876</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.8771</v>
+        <v>-2.2778</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3103</v>
+        <v>-0.4211</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.5668</v>
+        <v>-1.8567</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0674</v>
+        <v>-2.3468</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1992</v>
+        <v>-2.3468</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.4062</v>
+        <v>-5.5008</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.615</v>
+        <v>-3.5691</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7912</v>
+        <v>-1.9316</v>
       </c>
       <c r="G7" t="n">
         <v>0.3548</v>
@@ -1000,13 +1000,13 @@
         <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.8284</v>
+        <v>-2.9229</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8808</v>
+        <v>-0.835</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.9476</v>
+        <v>-2.088</v>
       </c>
       <c r="V7" t="n">
         <v>-1.7433</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. CORTES ANDRADES</t>
+          <t>F. MONTIEL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.5191</v>
+        <v>-5.8682</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5725</v>
+        <v>-4.4956</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9466</v>
+        <v>-1.3725</v>
       </c>
       <c r="G8" t="n">
-        <v>-6.5507</v>
+        <v>-2.9963</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.5379</v>
+        <v>1.0595</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0128</v>
+        <v>-4.0559</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.564</v>
+        <v>-1.6338</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.6845</v>
+        <v>0.9622000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1205</v>
+        <v>-2.596</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.9867</v>
+        <v>-1.3625</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8534</v>
+        <v>0.0973</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1333</v>
+        <v>-1.4599</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3876</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1982</v>
+        <v>-3.1716</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-2.0878</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0769</v>
+        <v>-0.8973</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5456</v>
+        <v>-1.1905</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2666</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. MONTIEL RODRIGUEZ</t>
+          <t>D. CORTES ANDRADES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.705</v>
+        <v>-6.174</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4167</v>
+        <v>-4.0589</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2883</v>
+        <v>-2.1151</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9963</v>
+        <v>-6.5507</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0595</v>
+        <v>-4.5379</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.0559</v>
+        <v>-2.0128</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.6338</v>
+        <v>-3.564</v>
       </c>
       <c r="K9" t="n">
-        <v>0.9622000000000001</v>
+        <v>-3.6845</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.596</v>
+        <v>0.1205</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3625</v>
+        <v>-2.9867</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0973</v>
+        <v>-0.8534</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4599</v>
+        <v>-2.1333</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3876</v>
+        <v>1.3876</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1716</v>
+        <v>-0.1982</v>
       </c>
       <c r="R9" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.9246</v>
+        <v>-1.2774</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8184</v>
+        <v>-0.5633</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1062</v>
+        <v>-0.7141</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7611</v>
+        <v>-6.7986</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8944</v>
+        <v>-3.7072</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8667</v>
+        <v>-3.0913</v>
       </c>
       <c r="G10" t="n">
         <v>-4.5408</v>
@@ -1234,13 +1234,13 @@
         <v>1.5858</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.154</v>
+        <v>-2.1915</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0056</v>
+        <v>-0.8184</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1485</v>
+        <v>-1.3731</v>
       </c>
       <c r="V10" t="n">
         <v>-0.4627</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.1462</v>
+        <v>-7.642</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.495</v>
+        <v>-0.9627</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.6512</v>
+        <v>-6.6793</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4028</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.1279</v>
+        <v>-2.6237</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5599</v>
+        <v>-1.0277</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.568</v>
+        <v>-1.596</v>
       </c>
       <c r="V11" t="n">
         <v>-3.0208</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.7813</v>
+        <v>-10.7635</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.417999999999999</v>
+        <v>-8.372199999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3632</v>
+        <v>-2.3913</v>
       </c>
       <c r="G12" t="n">
         <v>-5.9318</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.4708</v>
+        <v>-2.4531</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6312</v>
+        <v>-0.5854</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8396</v>
+        <v>-1.8677</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-55.9552</v>
+        <v>-54.39540000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-30.6169</v>
+        <v>-29.0568</v>
       </c>
       <c r="F13" t="n">
         <v>-25.3382</v>
@@ -1435,7 +1435,7 @@
         <v>-21.4344</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.9766</v>
+        <v>-3.976599999999999</v>
       </c>
       <c r="I13" t="n">
         <v>-17.458</v>
@@ -1468,13 +1468,13 @@
         <v>14.8669</v>
       </c>
       <c r="S13" t="n">
-        <v>-24.8329</v>
+        <v>-23.2731</v>
       </c>
       <c r="T13" t="n">
-        <v>-9.285400000000001</v>
+        <v>-7.725700000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-15.5476</v>
+        <v>-15.5477</v>
       </c>
       <c r="V13" t="n">
         <v>-7.705299999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.4869</v>
+        <v>10.6438</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9983</v>
+        <v>6.1834</v>
       </c>
       <c r="F14" t="n">
-        <v>4.4885</v>
+        <v>4.4604</v>
       </c>
       <c r="G14" t="n">
         <v>7.2589</v>
@@ -1546,13 +1546,13 @@
         <v>2.1805</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9436</v>
+        <v>2.1006</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9567</v>
+        <v>1.1418</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9869</v>
+        <v>0.9588</v>
       </c>
       <c r="V14" t="n">
         <v>2.0772</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7734</v>
+        <v>10.2993</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0665</v>
+        <v>5.7609</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7069</v>
+        <v>4.5384</v>
       </c>
       <c r="G15" t="n">
         <v>7.1012</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4829</v>
+        <v>2.0088</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2776</v>
+        <v>0.972</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2053</v>
+        <v>1.0368</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9751</v>
+        <v>8.653</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3118</v>
+        <v>4.8212</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6633</v>
+        <v>3.8318</v>
       </c>
       <c r="G16" t="n">
         <v>5.1463</v>
@@ -1702,13 +1702,13 @@
         <v>1.9822</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9676</v>
+        <v>1.6454</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2644</v>
+        <v>0.7738</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7032</v>
+        <v>0.8717</v>
       </c>
       <c r="V16" t="n">
         <v>0.8701</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.0559</v>
+        <v>7.1088</v>
       </c>
       <c r="E17" t="n">
-        <v>4.6608</v>
+        <v>4.9664</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3951</v>
+        <v>2.1424</v>
       </c>
       <c r="G17" t="n">
         <v>3.063</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>2.658</v>
+        <v>2.7109</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4134</v>
+        <v>1.719</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2446</v>
+        <v>0.9919</v>
       </c>
       <c r="V17" t="n">
         <v>1.1367</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.4118</v>
+        <v>6.0533</v>
       </c>
       <c r="E18" t="n">
-        <v>5.266</v>
+        <v>4.6547</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1459</v>
+        <v>1.3986</v>
       </c>
       <c r="G18" t="n">
         <v>3.2722</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4151</v>
+        <v>2.0566</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2284</v>
+        <v>1.6172</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1867</v>
+        <v>0.4395</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2666</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5.3015</v>
+        <v>5.1859</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4556</v>
+        <v>1.7612</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8459</v>
+        <v>3.4247</v>
       </c>
       <c r="G19" t="n">
         <v>1.7514</v>
@@ -1936,13 +1936,13 @@
         <v>2.1805</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0941</v>
+        <v>1.9785</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5985</v>
+        <v>0.9041</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4956</v>
+        <v>1.0745</v>
       </c>
       <c r="V19" t="n">
         <v>0.2666</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.9084</v>
+        <v>4.1892</v>
       </c>
       <c r="E20" t="n">
         <v>3.1361</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7723</v>
+        <v>1.0531</v>
       </c>
       <c r="G20" t="n">
         <v>0.1902</v>
@@ -2014,13 +2014,13 @@
         <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8392</v>
+        <v>2.12</v>
       </c>
       <c r="T20" t="n">
         <v>1.5492</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2899</v>
+        <v>0.5707</v>
       </c>
       <c r="V20" t="n">
         <v>2.0772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.9902</v>
+        <v>2.619</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8645</v>
+        <v>-1.1514</v>
       </c>
       <c r="F21" t="n">
-        <v>3.8546</v>
+        <v>3.7704</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3047</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9422</v>
+        <v>1.571</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2165</v>
+        <v>0.4966</v>
       </c>
       <c r="U21" t="n">
-        <v>1.1587</v>
+        <v>1.0745</v>
       </c>
       <c r="V21" t="n">
         <v>2.3438</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4547</v>
+        <v>0.7978</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7934</v>
+        <v>-1.5065</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2481</v>
+        <v>2.3042</v>
       </c>
       <c r="G22" t="n">
         <v>-2.413</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>3.4624</v>
+        <v>2.8055</v>
       </c>
       <c r="T22" t="n">
-        <v>2.7827</v>
+        <v>2.0696</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6797</v>
+        <v>0.7358</v>
       </c>
       <c r="V22" t="n">
         <v>0.6036</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.439</v>
+        <v>0.6532</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1675</v>
+        <v>-1.0656</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6065</v>
+        <v>1.7188</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7861</v>
@@ -2248,13 +2248,13 @@
         <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>2.9565</v>
+        <v>3.1707</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2394</v>
+        <v>2.3413</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7171</v>
+        <v>0.8294</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1367</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.157</v>
+        <v>0.6403</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4717</v>
+        <v>0.2413</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3147</v>
+        <v>0.399</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7504999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0.5947</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2654</v>
+        <v>1.0627</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1469</v>
+        <v>0.8599</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1186</v>
+        <v>0.2028</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2666</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6847</v>
+        <v>-0.8885</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2599</v>
+        <v>-2.4636</v>
       </c>
       <c r="F25" t="n">
         <v>1.5751</v>
@@ -2404,10 +2404,10 @@
         <v>0.5947</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8061</v>
+        <v>1.6023</v>
       </c>
       <c r="T25" t="n">
-        <v>1.3069</v>
+        <v>1.1032</v>
       </c>
       <c r="U25" t="n">
         <v>0.4992</v>
@@ -2437,7 +2437,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>55.9552</v>
+        <v>55.95510000000001</v>
       </c>
       <c r="E26" t="n">
         <v>25.3381</v>
@@ -2482,13 +2482,13 @@
         <v>16.8491</v>
       </c>
       <c r="S26" t="n">
-        <v>24.8331</v>
+        <v>24.833</v>
       </c>
       <c r="T26" t="n">
-        <v>15.5476</v>
+        <v>15.5477</v>
       </c>
       <c r="U26" t="n">
-        <v>9.285500000000003</v>
+        <v>9.285600000000001</v>
       </c>
       <c r="V26" t="n">
         <v>7.705299999999998</v>
